--- a/Data/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4218FBB9-74AA-4B6C-BB08-1E80D9087048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4C6F31-2406-4E31-9040-B961A0AA6132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="209">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,12 +213,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10697458</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>519 Recruitment (Zerab Sepupu (9575064) (Inherited))</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
     <t>UkOne</t>
   </si>
   <si>
-    <t>TwentyFiveMarchTenB</t>
-  </si>
-  <si>
     <t>161 923 4772</t>
   </si>
   <si>
@@ -345,9 +336,6 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10697459</t>
-  </si>
-  <si>
     <t>519 Store Management (Zerab Sepupu (9575064))</t>
   </si>
   <si>
@@ -375,12 +363,6 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>Test failed for 'UkThree TwentyFiveMarchTenB' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-03-10T13-45-36-343Z.png</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>UkThree</t>
   </si>
   <si>
@@ -399,9 +381,6 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>10697460</t>
-  </si>
-  <si>
     <t>UkFour</t>
   </si>
   <si>
@@ -429,9 +408,6 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>Test failed for 'UkFiveA TwentyFiveMarchTenB' Employee: Errors and AlertsErrorNational ID Type (Row 1 Column 4)The field National ID Type is required and must have a value. &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-03-10T14-01-18-573Z.png</t>
-  </si>
-  <si>
     <t>UkFiveA</t>
   </si>
   <si>
@@ -456,12 +432,6 @@
     <t>Test6</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'UkSix TwentyFiveMarchTenB' Employee:{10697461}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Propose Compensation Hire:  UkSix TwentyFiveMarchTenB')[22m
-</t>
-  </si>
-  <si>
     <t>UkSix</t>
   </si>
   <si>
@@ -483,9 +453,6 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10697462</t>
-  </si>
-  <si>
     <t>UkSeven</t>
   </si>
   <si>
@@ -507,9 +474,6 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10697463</t>
-  </si>
-  <si>
     <t>UkEight</t>
   </si>
   <si>
@@ -522,9 +486,6 @@
     <t>Test9</t>
   </si>
   <si>
-    <t>10697464</t>
-  </si>
-  <si>
     <t>UkNine</t>
   </si>
   <si>
@@ -546,9 +507,6 @@
     <t>Test10</t>
   </si>
   <si>
-    <t>10697465</t>
-  </si>
-  <si>
     <t>UkTen</t>
   </si>
   <si>
@@ -564,9 +522,6 @@
     <t>Test11</t>
   </si>
   <si>
-    <t>Test failed for 'UkEleven TwentyFiveMarchTenB' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-03-10T14-38-32-502Z.png</t>
-  </si>
-  <si>
     <t>UkEleven</t>
   </si>
   <si>
@@ -579,9 +534,6 @@
     <t>Test12</t>
   </si>
   <si>
-    <t>10697466</t>
-  </si>
-  <si>
     <t>UkTwelve</t>
   </si>
   <si>
@@ -594,9 +546,6 @@
     <t>Test13</t>
   </si>
   <si>
-    <t>10697467</t>
-  </si>
-  <si>
     <t>457 Recruitment (Vyzeb Vizupe (9457836))</t>
   </si>
   <si>
@@ -657,9 +606,6 @@
     <t>Test14</t>
   </si>
   <si>
-    <t>10697468</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mr. </t>
   </si>
   <si>
@@ -690,9 +636,6 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>10697469</t>
-  </si>
-  <si>
     <t>UkFifteen</t>
   </si>
   <si>
@@ -712,6 +655,9 @@
   </si>
   <si>
     <t>Mixed/Multiple Ethnic Groups - White and Black Carribbean</t>
+  </si>
+  <si>
+    <t>TwentyFiveAprilOne</t>
   </si>
 </sst>
 </file>
@@ -1558,71 +1504,66 @@
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="J2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>68</v>
-      </c>
       <c r="K2" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L2" s="15">
         <v>45597</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N2" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="R2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="S2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="T2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="V2" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W2" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X16" si="0">L2</f>
@@ -1633,25 +1574,25 @@
         <v>45687</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AD2" s="23" t="s">
         <v>79</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD2" s="23" t="s">
-        <v>82</v>
       </c>
       <c r="AE2" s="24">
         <v>519</v>
       </c>
       <c r="AF2" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG2" s="25">
         <v>37.5</v>
@@ -1660,73 +1601,73 @@
         <v>37.5</v>
       </c>
       <c r="AI2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL2" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AM2" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="AK2" s="27" t="s">
+      <c r="AN2" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AO2" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AP2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AR2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AT2" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AP2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AU2" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AR2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS2" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT2" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU2" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV2" s="30">
         <v>35591</v>
       </c>
       <c r="AW2" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX2" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY2" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ2" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA2" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB2" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BC2" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" s="30" t="s">
+      <c r="BD2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE2" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC2" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE2" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF2" s="14">
         <v>601613</v>
@@ -1735,81 +1676,77 @@
         <v>31926819</v>
       </c>
       <c r="BH2" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI2" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J3" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L3" s="15">
         <v>45597</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N3" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="R3" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="S3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="T3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="V3" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S3" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T3" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V3" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W3" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X3" s="20">
         <f t="shared" si="0"/>
@@ -1820,19 +1757,19 @@
         <v>45687</v>
       </c>
       <c r="Z3" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AE3" s="24">
         <v>519</v>
@@ -1847,73 +1784,73 @@
         <v>40</v>
       </c>
       <c r="AI3" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ3" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL3" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL3" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM3" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS3" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT3" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU3" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS3" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT3" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="AU3" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV3" s="30">
         <v>35591</v>
       </c>
       <c r="AW3" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ3" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA3" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB3" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY3" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="BC3" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA3" s="30" t="s">
+      <c r="BD3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE3" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC3" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE3" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF3" s="14">
         <v>601613</v>
@@ -1922,81 +1859,77 @@
         <v>31926819</v>
       </c>
       <c r="BH3" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI3" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J4" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L4" s="15">
         <v>45597</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="R4" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="S4" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="T4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="V4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S4" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U4" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V4" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W4" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X4" s="20">
         <f t="shared" si="0"/>
@@ -2007,19 +1940,19 @@
         <v>45687</v>
       </c>
       <c r="Z4" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AE4" s="24">
         <v>519</v>
@@ -2034,73 +1967,73 @@
         <v>40</v>
       </c>
       <c r="AI4" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ4" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK4" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL4" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ4" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK4" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL4" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM4" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS4" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT4" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU4" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP4" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ4" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS4" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT4" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU4" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV4" s="30">
         <v>35591</v>
       </c>
       <c r="AW4" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ4" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA4" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB4" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY4" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BC4" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BD4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE4" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB4" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC4" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE4" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF4" s="14">
         <v>601613</v>
@@ -2109,84 +2042,80 @@
         <v>31926819</v>
       </c>
       <c r="BH4" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI4" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BJ4" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J5" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L5" s="15">
         <v>45597</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="R5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="T5" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="V5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U5" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V5" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W5" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X5" s="20">
         <f t="shared" si="0"/>
@@ -2197,19 +2126,19 @@
         <v>45687</v>
       </c>
       <c r="Z5" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="AB5" s="33" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="AC5" s="22" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AD5" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AE5" s="24">
         <v>519</v>
@@ -2224,74 +2153,74 @@
         <v>40</v>
       </c>
       <c r="AI5" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AJ5" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AK5" s="27">
         <f>L5+365</f>
         <v>45962</v>
       </c>
       <c r="AL5" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN5" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ5" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT5" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU5" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP5" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ5" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS5" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT5" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU5" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV5" s="30">
         <v>35591</v>
       </c>
       <c r="AW5" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ5" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA5" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB5" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY5" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ5" s="30" t="s">
+      <c r="BC5" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA5" s="30" t="s">
+      <c r="BD5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE5" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB5" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC5" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE5" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF5" s="14">
         <v>601613</v>
@@ -2300,90 +2229,86 @@
         <v>31926819</v>
       </c>
       <c r="BH5" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI5" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BJ5" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="BN5" s="32" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BO5" s="7" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J6" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L6" s="15">
         <v>45597</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="R6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="14" t="s">
+      <c r="S6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q6" s="14" t="s">
+      <c r="T6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U6" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R6" s="17" t="s">
+      <c r="V6" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T6" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V6" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W6" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X6" s="20">
         <f t="shared" si="0"/>
@@ -2394,19 +2319,19 @@
         <v>45687</v>
       </c>
       <c r="Z6" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC6" s="22" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="AD6" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE6" s="24">
         <v>519</v>
@@ -2421,73 +2346,73 @@
         <v>40</v>
       </c>
       <c r="AI6" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ6" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK6" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK6" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL6" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM6" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN6" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS6" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT6" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU6" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ6" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR6" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT6" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="AU6" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV6" s="30">
         <v>35591</v>
       </c>
       <c r="AW6" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY6" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ6" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA6" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB6" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY6" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ6" s="30" t="s">
+      <c r="BC6" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA6" s="30" t="s">
+      <c r="BD6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE6" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB6" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC6" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD6" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE6" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF6" s="14">
         <v>601613</v>
@@ -2496,87 +2421,83 @@
         <v>31926819</v>
       </c>
       <c r="BH6" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI6" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BN6" s="7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J7" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L7" s="15">
         <v>45597</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="R7" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="S7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="T7" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="V7" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T7" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U7" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W7" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X7" s="20">
         <f t="shared" si="0"/>
@@ -2587,19 +2508,19 @@
         <v>45687</v>
       </c>
       <c r="Z7" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA7" s="21" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="AC7" s="22" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="AD7" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AE7" s="24">
         <v>519</v>
@@ -2614,74 +2535,74 @@
         <v>40</v>
       </c>
       <c r="AI7" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AJ7" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AK7" s="27">
         <f>L7+365</f>
         <v>45962</v>
       </c>
       <c r="AL7" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN7" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS7" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT7" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU7" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP7" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ7" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS7" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT7" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="AU7" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV7" s="30">
         <v>35591</v>
       </c>
       <c r="AW7" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY7" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ7" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA7" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB7" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY7" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ7" s="30" t="s">
+      <c r="BC7" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA7" s="30" t="s">
+      <c r="BD7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE7" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB7" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC7" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE7" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF7" s="14">
         <v>601613</v>
@@ -2690,87 +2611,83 @@
         <v>31926819</v>
       </c>
       <c r="BH7" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI7" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BN7" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="BO7" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J8" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L8" s="15">
         <v>45597</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N8" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="R8" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="S8" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="T8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U8" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="17" t="s">
+      <c r="V8" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U8" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V8" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W8" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X8" s="20">
         <f t="shared" si="0"/>
@@ -2781,19 +2698,19 @@
         <v>45687</v>
       </c>
       <c r="Z8" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC8" s="22" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE8" s="24">
         <v>519</v>
@@ -2808,73 +2725,73 @@
         <v>40</v>
       </c>
       <c r="AI8" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ8" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK8" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK8" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL8" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM8" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN8" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS8" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU8" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS8" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT8" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="AU8" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV8" s="30">
         <v>35591</v>
       </c>
       <c r="AW8" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX8" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY8" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ8" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA8" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB8" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY8" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ8" s="30" t="s">
+      <c r="BC8" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA8" s="30" t="s">
+      <c r="BD8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE8" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB8" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC8" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE8" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF8" s="14">
         <v>601613</v>
@@ -2883,87 +2800,83 @@
         <v>31926819</v>
       </c>
       <c r="BH8" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI8" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BN8" s="7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="BO8" s="7" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J9" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L9" s="15">
         <v>45597</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N9" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="R9" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="S9" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="T9" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U9" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="17" t="s">
+      <c r="V9" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T9" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U9" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V9" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W9" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X9" s="20">
         <f t="shared" si="0"/>
@@ -2974,25 +2887,25 @@
         <v>45687</v>
       </c>
       <c r="Z9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC9" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="AA9" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC9" s="22" t="s">
-        <v>81</v>
-      </c>
       <c r="AD9" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE9" s="24">
         <v>519</v>
       </c>
       <c r="AF9" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG9" s="25">
         <v>15</v>
@@ -3001,73 +2914,73 @@
         <v>40</v>
       </c>
       <c r="AI9" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK9" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ9" s="23" t="s">
+      <c r="AM9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="AK9" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL9" s="14" t="s">
+      <c r="AN9" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AM9" s="14" t="s">
+      <c r="AP9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ9" s="10" t="s">
+      <c r="AR9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS9" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT9" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU9" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AR9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS9" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT9" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AU9" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV9" s="30">
         <v>35591</v>
       </c>
       <c r="AW9" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY9" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ9" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB9" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY9" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ9" s="30" t="s">
+      <c r="BC9" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA9" s="30" t="s">
+      <c r="BD9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE9" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB9" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC9" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE9" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF9" s="14">
         <v>601613</v>
@@ -3076,81 +2989,76 @@
         <v>31926819</v>
       </c>
       <c r="BH9" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI9" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C10" s="8"/>
       <c r="D10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J10" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L10" s="15">
         <v>45597</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q10" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="R10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="S10" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="T10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U10" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R10" s="17" t="s">
+      <c r="V10" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T10" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U10" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V10" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W10" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X10" s="20">
         <f t="shared" si="0"/>
@@ -3161,25 +3069,25 @@
         <v>45687</v>
       </c>
       <c r="Z10" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC10" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD10" s="23" t="s">
         <v>79</v>
-      </c>
-      <c r="AB10" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC10" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD10" s="23" t="s">
-        <v>82</v>
       </c>
       <c r="AE10" s="24">
         <v>519</v>
       </c>
       <c r="AF10" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG10" s="25">
         <v>37.5</v>
@@ -3188,73 +3096,73 @@
         <v>37.5</v>
       </c>
       <c r="AI10" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK10" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL10" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AM10" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="AK10" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL10" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM10" s="14" t="s">
+      <c r="AN10" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AO10" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ10" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN10" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO10" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="AP10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="AQ10" s="10" t="s">
+      <c r="AR10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS10" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT10" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="AU10" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AR10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS10" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT10" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="AU10" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV10" s="30">
         <v>35591</v>
       </c>
       <c r="AW10" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY10" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ10" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA10" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB10" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY10" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ10" s="30" t="s">
+      <c r="BC10" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA10" s="30" t="s">
+      <c r="BD10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE10" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB10" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC10" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE10" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF10" s="14">
         <v>601613</v>
@@ -3263,81 +3171,76 @@
         <v>31926819</v>
       </c>
       <c r="BH10" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI10" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J11" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L11" s="15">
         <v>45597</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="R11" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="S11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q11" s="14" t="s">
+      <c r="T11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U11" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R11" s="17" t="s">
+      <c r="V11" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T11" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W11" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X11" s="20">
         <f t="shared" si="0"/>
@@ -3348,25 +3251,25 @@
         <v>45687</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA11" s="21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC11" s="22" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE11" s="24">
         <v>519</v>
       </c>
       <c r="AF11" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG11" s="25">
         <v>16</v>
@@ -3375,73 +3278,73 @@
         <v>40</v>
       </c>
       <c r="AI11" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ11" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK11" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ11" s="23" t="s">
+      <c r="AM11" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="AK11" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL11" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM11" s="14" t="s">
+      <c r="AN11" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO11" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AN11" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="AO11" s="7" t="s">
+      <c r="AP11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS11" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT11" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU11" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP11" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ11" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR11" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS11" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT11" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="AU11" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV11" s="30">
         <v>35591</v>
       </c>
       <c r="AW11" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY11" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ11" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA11" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB11" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY11" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ11" s="30" t="s">
+      <c r="BC11" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA11" s="30" t="s">
+      <c r="BD11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE11" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB11" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC11" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD11" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE11" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF11" s="14">
         <v>601613</v>
@@ -3450,81 +3353,76 @@
         <v>31926819</v>
       </c>
       <c r="BH11" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI11" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C12" s="8"/>
       <c r="D12" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J12" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L12" s="15">
         <v>45597</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="R12" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P12" s="14" t="s">
+      <c r="S12" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q12" s="14" t="s">
+      <c r="T12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R12" s="17" t="s">
+      <c r="V12" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U12" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V12" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W12" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X12" s="20">
         <f t="shared" si="0"/>
@@ -3535,19 +3433,19 @@
         <v>45687</v>
       </c>
       <c r="Z12" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AB12" s="33" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="AC12" s="22" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE12" s="24">
         <v>519</v>
@@ -3562,74 +3460,74 @@
         <v>40</v>
       </c>
       <c r="AI12" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AJ12" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AK12" s="27">
         <f>L12+365</f>
         <v>45962</v>
       </c>
       <c r="AL12" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM12" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN12" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS12" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT12" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="AU12" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ12" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS12" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT12" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU12" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV12" s="30">
         <v>35591</v>
       </c>
       <c r="AW12" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY12" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ12" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA12" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB12" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY12" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ12" s="30" t="s">
+      <c r="BC12" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA12" s="30" t="s">
+      <c r="BD12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE12" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB12" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC12" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE12" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF12" s="14">
         <v>601613</v>
@@ -3638,81 +3536,77 @@
         <v>31926819</v>
       </c>
       <c r="BH12" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI12" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I13" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="J13" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L13" s="15">
         <v>45597</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q13" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="R13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q13" s="14" t="s">
+      <c r="T13" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="U13" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="V13" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="V13" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="W13" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X13" s="20">
         <f t="shared" si="0"/>
@@ -3723,19 +3617,19 @@
         <v>45687</v>
       </c>
       <c r="Z13" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC13" s="22" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE13" s="24">
         <v>519</v>
@@ -3750,73 +3644,73 @@
         <v>40</v>
       </c>
       <c r="AI13" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ13" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK13" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ13" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK13" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL13" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM13" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AN13" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AO13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS13" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT13" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="AU13" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="AP13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ13" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR13" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS13" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT13" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="AU13" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV13" s="30">
         <v>35591</v>
       </c>
       <c r="AW13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY13" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ13" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA13" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB13" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY13" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ13" s="30" t="s">
+      <c r="BC13" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="BA13" s="30" t="s">
+      <c r="BD13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE13" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="BB13" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC13" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD13" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE13" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF13" s="14">
         <v>601613</v>
@@ -3825,87 +3719,83 @@
         <v>31926819</v>
       </c>
       <c r="BH13" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI13" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="BN13" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="BO13" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J14" s="36" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L14" s="15">
         <v>45597</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="T14" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U14" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="V14" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="W14" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X14" s="20">
         <f t="shared" si="0"/>
@@ -3916,19 +3806,19 @@
         <v>45687</v>
       </c>
       <c r="Z14" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA14" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB14" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC14" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="AA14" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB14" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC14" s="39" t="s">
-        <v>81</v>
-      </c>
       <c r="AD14" s="39" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AE14" s="40">
         <v>457</v>
@@ -3943,73 +3833,73 @@
         <v>40</v>
       </c>
       <c r="AI14" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ14" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK14" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL14" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ14" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK14" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL14" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM14" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN14" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO14" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP14" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ14" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN14" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="AO14" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="AP14" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="AQ14" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="AR14" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AS14" s="28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AT14" s="29" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="AU14" s="7" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AV14" s="30">
         <v>38081</v>
       </c>
       <c r="AW14" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="AZ14" s="30" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BA14" s="30">
         <v>45020</v>
       </c>
       <c r="BB14" s="45" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="BC14" s="46" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="BD14" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BE14" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="BF14" s="44">
         <v>200052</v>
@@ -4018,81 +3908,77 @@
         <v>75849856</v>
       </c>
       <c r="BH14" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI14" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F15" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="I15" s="36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L15" s="15">
         <v>45597</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="V15" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X15" s="20">
         <f t="shared" si="0"/>
@@ -4103,25 +3989,25 @@
         <v>45687</v>
       </c>
       <c r="Z15" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA15" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB15" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC15" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="AA15" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB15" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC15" s="47" t="s">
-        <v>81</v>
-      </c>
       <c r="AD15" s="39" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="AE15" s="40">
         <v>457</v>
       </c>
       <c r="AF15" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG15" s="41">
         <v>25</v>
@@ -4130,74 +4016,74 @@
         <v>40</v>
       </c>
       <c r="AI15" s="42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AJ15" s="39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AK15" s="27">
         <f>L15+365</f>
         <v>45962</v>
       </c>
       <c r="AL15" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM15" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN15" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="AO15" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP15" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ15" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN15" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="AO15" s="39" t="s">
+      <c r="AR15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS15" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT15" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AU15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV15" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="AP15" s="39" t="s">
+      <c r="AW15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AX15" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY15" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ15" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="AQ15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS15" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT15" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="AU15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV15" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX15" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="AY15" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="AZ15" s="30" t="s">
-        <v>215</v>
-      </c>
       <c r="BA15" s="30" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="BB15" s="45" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="BC15" s="46" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="BD15" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BE15" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="BF15" s="44">
         <v>200052</v>
@@ -4206,81 +4092,76 @@
         <v>75849858</v>
       </c>
       <c r="BH15" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI15" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="I16" s="36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L16" s="15">
         <v>45597</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="S16" s="14" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="T16" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U16" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="V16" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="W16" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X16" s="20">
         <f t="shared" si="0"/>
@@ -4291,19 +4172,19 @@
         <v>45687</v>
       </c>
       <c r="Z16" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA16" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB16" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC16" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="AA16" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB16" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC16" s="47" t="s">
-        <v>81</v>
-      </c>
       <c r="AD16" s="39" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="AE16" s="40">
         <v>457</v>
@@ -4318,74 +4199,74 @@
         <v>37.5</v>
       </c>
       <c r="AI16" s="42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AJ16" s="39" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AK16" s="27">
         <f>L16+365</f>
         <v>45962</v>
       </c>
       <c r="AL16" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM16" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN16" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO16" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP16" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AN16" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="AO16" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="AP16" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="AQ16" s="10" t="s">
+      <c r="AR16" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS16" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT16" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="AU16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AR16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS16" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT16" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="AU16" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="AV16" s="30" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="AW16" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="AZ16" s="30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="BA16" s="30">
         <v>44197</v>
       </c>
       <c r="BB16" s="45" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="BC16" s="46" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="BD16" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BE16" s="10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="BF16" s="44">
         <v>200052</v>
@@ -4394,10 +4275,10 @@
         <v>75849861</v>
       </c>
       <c r="BH16" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BI16" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="46:46" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
